--- a/VerveStacks_NOR_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
+++ b/VerveStacks_NOR_grids_kan50/SuppXLS/Scen_TSParameters_ts_12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan50\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{742C1E54-2582-4F71-B9BF-ED408B0E1FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1292D8A3-1BF4-4E11-A0A6-956084365730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4012" yWindow="4012" windowWidth="21601" windowHeight="11423" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3915" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3923" uniqueCount="238">
   <si>
     <t>share of charging at night</t>
   </si>
@@ -720,19 +720,22 @@
     <t>D</t>
   </si>
   <si>
-    <t>S2aH2,S4aH2,S3aH2,S1aH2</t>
+    <t>S2aH2,S3aH2,S4aH2,S1aH2</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S3aH3,S4aH1,S2aH1,S2aH3,S1aH1,S4aH3,S3aH1,S1aH3</t>
+    <t>S3aH3,S4aH1,S2aH3,S1aH1,S4aH3,S3aH1,S2aH1,S1aH3</t>
   </si>
   <si>
     <t>elc_buildings</t>
   </si>
   <si>
     <t>elc_industry</t>
+  </si>
+  <si>
+    <t>het_buildings</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -1292,7 +1295,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S3aH3,S4aH1,S2aH1,S2aH3,S1aH1,S4aH3,S3aH1,S1aH3</v>
+        <v>S3aH3,S4aH1,S2aH3,S1aH1,S4aH3,S3aH1,S2aH1,S1aH3</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1324,7 +1327,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S2aH2,S4aH2,S3aH2,S1aH2</v>
+        <v>S2aH2,S3aH2,S4aH2,S1aH2</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1431,7 +1434,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26CF916A-B613-4FBD-B555-A73856C2246B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B3EBCE2-BF7E-46B0-AA88-287F7AF38C84}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1511,7 +1514,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2FA0394-327A-4994-8DD6-B0B8AF5F9DA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B2B82AA-6E99-4466-9A5B-44FC2AC1141A}">
   <dimension ref="B9:O442"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12661,7 +12664,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAED80FA-9970-4A89-9C31-371E8A42AF99}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A32EA06-B0A8-4B56-A4C4-CCE8A875A67C}">
   <dimension ref="B9:CI81"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -28655,7 +28658,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09F99F28-6549-48F2-83C7-0682DA301F2F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE6E2253-A060-4B90-BEF5-0D7F145113E6}">
   <dimension ref="A9:S126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -28709,19 +28712,19 @@
         <v>49</v>
       </c>
       <c r="N10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q10" t="s">
         <v>49</v>
       </c>
       <c r="R10" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="S10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.45">
@@ -28765,7 +28768,7 @@
         <v>0.51333333333333331</v>
       </c>
       <c r="S11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.45">
@@ -28809,7 +28812,7 @@
         <v>0.48293333333333327</v>
       </c>
       <c r="S12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.45">
@@ -28853,7 +28856,7 @@
         <v>0.40433333333333338</v>
       </c>
       <c r="S13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.45">
@@ -28897,7 +28900,7 @@
         <v>0.4665333333333333</v>
       </c>
       <c r="S14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.45">
@@ -28941,7 +28944,7 @@
         <v>0.5678333333333333</v>
       </c>
       <c r="S15" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.45">
@@ -28985,7 +28988,7 @@
         <v>0.44270000000000004</v>
       </c>
       <c r="S16" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" spans="3:19" x14ac:dyDescent="0.45">
@@ -29029,7 +29032,7 @@
         <v>0.37896666666666667</v>
       </c>
       <c r="S17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="18" spans="3:19" x14ac:dyDescent="0.45">
@@ -29073,7 +29076,7 @@
         <v>0.43433333333333329</v>
       </c>
       <c r="S18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="3:19" x14ac:dyDescent="0.45">
@@ -29117,7 +29120,7 @@
         <v>0.49553333333333333</v>
       </c>
       <c r="S19" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="20" spans="3:19" x14ac:dyDescent="0.45">
@@ -29161,7 +29164,7 @@
         <v>0.42123333333333335</v>
       </c>
       <c r="S20" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="21" spans="3:19" x14ac:dyDescent="0.45">
@@ -29205,7 +29208,7 @@
         <v>0.39156666666666667</v>
       </c>
       <c r="S21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="3:19" x14ac:dyDescent="0.45">
@@ -29249,7 +29252,7 @@
         <v>0.38286666666666669</v>
       </c>
       <c r="S22" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="3:19" x14ac:dyDescent="0.45">
@@ -29272,7 +29275,7 @@
         <v>0.68703333333333327</v>
       </c>
       <c r="S23" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="3:19" x14ac:dyDescent="0.45">
@@ -29295,7 +29298,7 @@
         <v>0.57043333333333335</v>
       </c>
       <c r="S24" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="3:19" x14ac:dyDescent="0.45">
@@ -29318,7 +29321,7 @@
         <v>0.51189999999999991</v>
       </c>
       <c r="S25" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="26" spans="3:19" x14ac:dyDescent="0.45">
@@ -29341,7 +29344,7 @@
         <v>0.57546666666666668</v>
       </c>
       <c r="S26" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27" spans="3:19" x14ac:dyDescent="0.45">
@@ -29364,7 +29367,7 @@
         <v>0.50803333333333323</v>
       </c>
       <c r="S27" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="28" spans="3:19" x14ac:dyDescent="0.45">
@@ -29387,7 +29390,7 @@
         <v>0.42379999999999995</v>
       </c>
       <c r="S28" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29" spans="3:19" x14ac:dyDescent="0.45">
@@ -29410,7 +29413,7 @@
         <v>0.39040000000000002</v>
       </c>
       <c r="S29" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" spans="3:19" x14ac:dyDescent="0.45">
@@ -29433,7 +29436,7 @@
         <v>0.41570000000000001</v>
       </c>
       <c r="S30" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="31" spans="3:19" x14ac:dyDescent="0.45">
@@ -29456,7 +29459,7 @@
         <v>0.67649999999999999</v>
       </c>
       <c r="S31" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="32" spans="3:19" x14ac:dyDescent="0.45">
@@ -29479,7 +29482,7 @@
         <v>0.56376666666666664</v>
       </c>
       <c r="S32" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="33" spans="8:19" x14ac:dyDescent="0.45">
@@ -29502,7 +29505,7 @@
         <v>0.46443333333333331</v>
       </c>
       <c r="S33" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="34" spans="8:19" x14ac:dyDescent="0.45">
@@ -29525,10 +29528,19 @@
         <v>0.54683333333333328</v>
       </c>
       <c r="S34" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="35" spans="8:19" x14ac:dyDescent="0.45">
+      <c r="H35" t="s">
+        <v>232</v>
+      </c>
+      <c r="I35" t="s">
+        <v>38</v>
+      </c>
+      <c r="J35">
+        <v>0.406113</v>
+      </c>
       <c r="P35">
         <v>2028</v>
       </c>
@@ -29539,10 +29551,19 @@
         <v>0.64013333333333333</v>
       </c>
       <c r="S35" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="36" spans="8:19" x14ac:dyDescent="0.45">
+      <c r="H36" t="s">
+        <v>232</v>
+      </c>
+      <c r="I36" t="s">
+        <v>42</v>
+      </c>
+      <c r="J36">
+        <v>0.27523599999999998</v>
+      </c>
       <c r="P36">
         <v>2028</v>
       </c>
@@ -29553,10 +29574,19 @@
         <v>0.52859999999999996</v>
       </c>
       <c r="S36" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="37" spans="8:19" x14ac:dyDescent="0.45">
+      <c r="H37" t="s">
+        <v>232</v>
+      </c>
+      <c r="I37" t="s">
+        <v>44</v>
+      </c>
+      <c r="J37">
+        <v>8.2413E-2</v>
+      </c>
       <c r="P37">
         <v>2028</v>
       </c>
@@ -29567,10 +29597,19 @@
         <v>0.4830666666666667</v>
       </c>
       <c r="S37" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="38" spans="8:19" x14ac:dyDescent="0.45">
+      <c r="H38" t="s">
+        <v>232</v>
+      </c>
+      <c r="I38" t="s">
+        <v>46</v>
+      </c>
+      <c r="J38">
+        <v>0.236239</v>
+      </c>
       <c r="P38">
         <v>2028</v>
       </c>
@@ -29581,7 +29620,7 @@
         <v>0.58586666666666665</v>
       </c>
       <c r="S38" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39" spans="8:19" x14ac:dyDescent="0.45">
@@ -29595,7 +29634,7 @@
         <v>0.63506666666666678</v>
       </c>
       <c r="S39" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40" spans="8:19" x14ac:dyDescent="0.45">
@@ -29609,7 +29648,7 @@
         <v>0.54619999999999991</v>
       </c>
       <c r="S40" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="41" spans="8:19" x14ac:dyDescent="0.45">
@@ -29623,7 +29662,7 @@
         <v>0.4548666666666667</v>
       </c>
       <c r="S41" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="42" spans="8:19" x14ac:dyDescent="0.45">
@@ -29637,7 +29676,7 @@
         <v>0.53326666666666667</v>
       </c>
       <c r="S42" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43" spans="8:19" x14ac:dyDescent="0.45">
@@ -29651,7 +29690,7 @@
         <v>0.64080000000000004</v>
       </c>
       <c r="S43" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="44" spans="8:19" x14ac:dyDescent="0.45">
@@ -29665,7 +29704,7 @@
         <v>0.53003333333333336</v>
       </c>
       <c r="S44" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="45" spans="8:19" x14ac:dyDescent="0.45">
@@ -29679,7 +29718,7 @@
         <v>0.41166666666666663</v>
       </c>
       <c r="S45" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="46" spans="8:19" x14ac:dyDescent="0.45">
@@ -29690,10 +29729,10 @@
         <v>46</v>
       </c>
       <c r="R46">
-        <v>0.5126666666666666</v>
+        <v>0.51266666666666671</v>
       </c>
       <c r="S46" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="47" spans="8:19" x14ac:dyDescent="0.45">
@@ -29707,7 +29746,7 @@
         <v>0.58139999999999992</v>
       </c>
       <c r="S47" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="48" spans="8:19" x14ac:dyDescent="0.45">
@@ -29721,7 +29760,7 @@
         <v>0.4685333333333333</v>
       </c>
       <c r="S48" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="49" spans="16:19" x14ac:dyDescent="0.45">
@@ -29735,7 +29774,7 @@
         <v>0.41726666666666662</v>
       </c>
       <c r="S49" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="50" spans="16:19" x14ac:dyDescent="0.45">
@@ -29749,7 +29788,7 @@
         <v>0.44283333333333336</v>
       </c>
       <c r="S50" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="51" spans="16:19" x14ac:dyDescent="0.45">
@@ -29763,7 +29802,7 @@
         <v>0.64950000000000008</v>
       </c>
       <c r="S51" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="52" spans="16:19" x14ac:dyDescent="0.45">
@@ -29777,7 +29816,7 @@
         <v>0.52576666666666672</v>
       </c>
       <c r="S52" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="53" spans="16:19" x14ac:dyDescent="0.45">
@@ -29791,7 +29830,7 @@
         <v>0.38569999999999999</v>
       </c>
       <c r="S53" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="54" spans="16:19" x14ac:dyDescent="0.45">
@@ -29805,7 +29844,7 @@
         <v>0.48826666666666663</v>
       </c>
       <c r="S54" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="55" spans="16:19" x14ac:dyDescent="0.45">
@@ -29819,7 +29858,7 @@
         <v>0.59670000000000001</v>
       </c>
       <c r="S55" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="56" spans="16:19" x14ac:dyDescent="0.45">
@@ -29833,7 +29872,7 @@
         <v>0.49499999999999994</v>
       </c>
       <c r="S56" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="57" spans="16:19" x14ac:dyDescent="0.45">
@@ -29847,7 +29886,7 @@
         <v>0.40076666666666672</v>
       </c>
       <c r="S57" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="58" spans="16:19" x14ac:dyDescent="0.45">
@@ -29858,10 +29897,10 @@
         <v>46</v>
       </c>
       <c r="R58">
-        <v>0.52036666666666664</v>
+        <v>0.52036666666666676</v>
       </c>
       <c r="S58" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="59" spans="16:19" x14ac:dyDescent="0.45">
@@ -29875,7 +29914,7 @@
         <v>0.65393333333333326</v>
       </c>
       <c r="S59" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="60" spans="16:19" x14ac:dyDescent="0.45">
@@ -29889,7 +29928,7 @@
         <v>0.47013333333333329</v>
       </c>
       <c r="S60" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="61" spans="16:19" x14ac:dyDescent="0.45">
@@ -29903,7 +29942,7 @@
         <v>0.45906666666666668</v>
       </c>
       <c r="S61" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="62" spans="16:19" x14ac:dyDescent="0.45">
@@ -29914,10 +29953,10 @@
         <v>46</v>
       </c>
       <c r="R62">
-        <v>0.46543333333333331</v>
+        <v>0.46543333333333337</v>
       </c>
       <c r="S62" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="63" spans="16:19" x14ac:dyDescent="0.45">
@@ -29931,7 +29970,7 @@
         <v>0.57210000000000005</v>
       </c>
       <c r="S63" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="64" spans="16:19" x14ac:dyDescent="0.45">
@@ -29945,7 +29984,7 @@
         <v>0.47480000000000006</v>
       </c>
       <c r="S64" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="65" spans="16:19" x14ac:dyDescent="0.45">
@@ -29959,7 +29998,7 @@
         <v>0.40796666666666664</v>
       </c>
       <c r="S65" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="66" spans="16:19" x14ac:dyDescent="0.45">
@@ -29973,7 +30012,7 @@
         <v>0.4841333333333333</v>
       </c>
       <c r="S66" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="67" spans="16:19" x14ac:dyDescent="0.45">
@@ -29987,7 +30026,7 @@
         <v>0.58056666666666668</v>
       </c>
       <c r="S67" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="68" spans="16:19" x14ac:dyDescent="0.45">
@@ -30001,7 +30040,7 @@
         <v>0.53960000000000008</v>
       </c>
       <c r="S68" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="69" spans="16:19" x14ac:dyDescent="0.45">
@@ -30015,7 +30054,7 @@
         <v>0.4041333333333334</v>
       </c>
       <c r="S69" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="70" spans="16:19" x14ac:dyDescent="0.45">
@@ -30029,7 +30068,7 @@
         <v>0.46510000000000001</v>
       </c>
       <c r="S70" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="71" spans="16:19" x14ac:dyDescent="0.45">
@@ -30043,7 +30082,7 @@
         <v>0.53883333333333328</v>
       </c>
       <c r="S71" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="72" spans="16:19" x14ac:dyDescent="0.45">
@@ -30057,7 +30096,7 @@
         <v>0.44576666666666664</v>
       </c>
       <c r="S72" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="73" spans="16:19" x14ac:dyDescent="0.45">
@@ -30071,7 +30110,7 @@
         <v>0.45049999999999996</v>
       </c>
       <c r="S73" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="74" spans="16:19" x14ac:dyDescent="0.45">
@@ -30085,7 +30124,7 @@
         <v>0.46469999999999995</v>
       </c>
       <c r="S74" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="75" spans="16:19" x14ac:dyDescent="0.45">
@@ -30099,7 +30138,7 @@
         <v>0.56063333333333332</v>
       </c>
       <c r="S75" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="76" spans="16:19" x14ac:dyDescent="0.45">
@@ -30113,7 +30152,7 @@
         <v>0.49706666666666671</v>
       </c>
       <c r="S76" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="77" spans="16:19" x14ac:dyDescent="0.45">
@@ -30127,7 +30166,7 @@
         <v>0.39463333333333334</v>
       </c>
       <c r="S77" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="78" spans="16:19" x14ac:dyDescent="0.45">
@@ -30138,10 +30177,10 @@
         <v>46</v>
       </c>
       <c r="R78">
-        <v>0.50383333333333324</v>
+        <v>0.50383333333333336</v>
       </c>
       <c r="S78" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="79" spans="16:19" x14ac:dyDescent="0.45">
@@ -30155,7 +30194,7 @@
         <v>0.60343333333333338</v>
       </c>
       <c r="S79" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="80" spans="16:19" x14ac:dyDescent="0.45">
@@ -30169,7 +30208,7 @@
         <v>0.45140000000000002</v>
       </c>
       <c r="S80" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="81" spans="16:19" x14ac:dyDescent="0.45">
@@ -30183,7 +30222,7 @@
         <v>0.39076666666666665</v>
       </c>
       <c r="S81" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="82" spans="16:19" x14ac:dyDescent="0.45">
@@ -30194,10 +30233,10 @@
         <v>46</v>
       </c>
       <c r="R82">
-        <v>0.48076666666666662</v>
+        <v>0.48076666666666673</v>
       </c>
       <c r="S82" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="83" spans="16:19" x14ac:dyDescent="0.45">
@@ -30211,7 +30250,7 @@
         <v>0.5806</v>
       </c>
       <c r="S83" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="84" spans="16:19" x14ac:dyDescent="0.45">
@@ -30225,7 +30264,7 @@
         <v>0.44943333333333335</v>
       </c>
       <c r="S84" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="85" spans="16:19" x14ac:dyDescent="0.45">
@@ -30239,7 +30278,7 @@
         <v>0.38366666666666666</v>
       </c>
       <c r="S85" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="86" spans="16:19" x14ac:dyDescent="0.45">
@@ -30253,7 +30292,7 @@
         <v>0.48770000000000002</v>
       </c>
       <c r="S86" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="87" spans="16:19" x14ac:dyDescent="0.45">
@@ -30267,7 +30306,7 @@
         <v>0.48920000000000002</v>
       </c>
       <c r="S87" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="88" spans="16:19" x14ac:dyDescent="0.45">
@@ -30281,7 +30320,7 @@
         <v>0.45343333333333335</v>
       </c>
       <c r="S88" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="89" spans="16:19" x14ac:dyDescent="0.45">
@@ -30295,7 +30334,7 @@
         <v>0.37609999999999993</v>
       </c>
       <c r="S89" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="90" spans="16:19" x14ac:dyDescent="0.45">
@@ -30309,7 +30348,7 @@
         <v>0.46283333333333337</v>
       </c>
       <c r="S90" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="91" spans="16:19" x14ac:dyDescent="0.45">
@@ -30323,7 +30362,7 @@
         <v>0.46300000000000002</v>
       </c>
       <c r="S91" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="92" spans="16:19" x14ac:dyDescent="0.45">
@@ -30337,7 +30376,7 @@
         <v>0.40473333333333333</v>
       </c>
       <c r="S92" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="93" spans="16:19" x14ac:dyDescent="0.45">
@@ -30351,7 +30390,7 @@
         <v>0.37336666666666662</v>
       </c>
       <c r="S93" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="94" spans="16:19" x14ac:dyDescent="0.45">
@@ -30365,7 +30404,7 @@
         <v>0.40809999999999996</v>
       </c>
       <c r="S94" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="95" spans="16:19" x14ac:dyDescent="0.45">
@@ -30379,7 +30418,7 @@
         <v>0.53733333333333333</v>
       </c>
       <c r="S95" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="96" spans="16:19" x14ac:dyDescent="0.45">
@@ -30393,7 +30432,7 @@
         <v>0.43103333333333332</v>
       </c>
       <c r="S96" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="97" spans="16:19" x14ac:dyDescent="0.45">
@@ -30407,7 +30446,7 @@
         <v>0.42219999999999996</v>
       </c>
       <c r="S97" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="98" spans="16:19" x14ac:dyDescent="0.45">
@@ -30421,7 +30460,7 @@
         <v>0.40806666666666663</v>
       </c>
       <c r="S98" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="99" spans="16:19" x14ac:dyDescent="0.45">
@@ -30435,7 +30474,7 @@
         <v>0.5379666666666667</v>
       </c>
       <c r="S99" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="100" spans="16:19" x14ac:dyDescent="0.45">
@@ -30449,7 +30488,7 @@
         <v>0.47150000000000003</v>
       </c>
       <c r="S100" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="101" spans="16:19" x14ac:dyDescent="0.45">
@@ -30463,7 +30502,7 @@
         <v>0.43759999999999999</v>
       </c>
       <c r="S101" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="102" spans="16:19" x14ac:dyDescent="0.45">
@@ -30477,7 +30516,7 @@
         <v>0.44026666666666664</v>
       </c>
       <c r="S102" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="103" spans="16:19" x14ac:dyDescent="0.45">
@@ -30491,7 +30530,7 @@
         <v>0.4879</v>
       </c>
       <c r="S103" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="104" spans="16:19" x14ac:dyDescent="0.45">
@@ -30505,7 +30544,7 @@
         <v>0.48726666666666674</v>
       </c>
       <c r="S104" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="105" spans="16:19" x14ac:dyDescent="0.45">
@@ -30519,7 +30558,7 @@
         <v>0.38966666666666666</v>
       </c>
       <c r="S105" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="106" spans="16:19" x14ac:dyDescent="0.45">
@@ -30533,7 +30572,7 @@
         <v>0.45116666666666666</v>
       </c>
       <c r="S106" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="107" spans="16:19" x14ac:dyDescent="0.45">
@@ -30547,7 +30586,7 @@
         <v>0.5623999999999999</v>
       </c>
       <c r="S107" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="108" spans="16:19" x14ac:dyDescent="0.45">
@@ -30561,7 +30600,7 @@
         <v>0.45389999999999997</v>
       </c>
       <c r="S108" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="109" spans="16:19" x14ac:dyDescent="0.45">
@@ -30575,7 +30614,7 @@
         <v>0.4237333333333333</v>
       </c>
       <c r="S109" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="110" spans="16:19" x14ac:dyDescent="0.45">
@@ -30589,7 +30628,7 @@
         <v>0.43369999999999997</v>
       </c>
       <c r="S110" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="111" spans="16:19" x14ac:dyDescent="0.45">
@@ -30603,7 +30642,7 @@
         <v>0.5672666666666667</v>
       </c>
       <c r="S111" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="112" spans="16:19" x14ac:dyDescent="0.45">
@@ -30617,7 +30656,7 @@
         <v>0.54373333333333329</v>
       </c>
       <c r="S112" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="113" spans="16:19" x14ac:dyDescent="0.45">
@@ -30631,7 +30670,7 @@
         <v>0.37453333333333338</v>
       </c>
       <c r="S113" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="114" spans="16:19" x14ac:dyDescent="0.45">
@@ -30645,7 +30684,7 @@
         <v>0.51946666666666663</v>
       </c>
       <c r="S114" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="115" spans="16:19" x14ac:dyDescent="0.45">
@@ -30659,7 +30698,7 @@
         <v>0.55986666666666662</v>
       </c>
       <c r="S115" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="116" spans="16:19" x14ac:dyDescent="0.45">
@@ -30673,7 +30712,7 @@
         <v>0.48806666666666665</v>
       </c>
       <c r="S116" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="117" spans="16:19" x14ac:dyDescent="0.45">
@@ -30687,7 +30726,7 @@
         <v>0.41326666666666667</v>
       </c>
       <c r="S117" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="118" spans="16:19" x14ac:dyDescent="0.45">
@@ -30698,10 +30737,10 @@
         <v>46</v>
       </c>
       <c r="R118">
-        <v>0.49659999999999993</v>
+        <v>0.49659999999999999</v>
       </c>
       <c r="S118" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="119" spans="16:19" x14ac:dyDescent="0.45">
@@ -30715,7 +30754,7 @@
         <v>0.58806666666666663</v>
       </c>
       <c r="S119" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="120" spans="16:19" x14ac:dyDescent="0.45">
@@ -30729,7 +30768,7 @@
         <v>0.47560000000000002</v>
       </c>
       <c r="S120" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="121" spans="16:19" x14ac:dyDescent="0.45">
@@ -30743,7 +30782,7 @@
         <v>0.47403333333333331</v>
       </c>
       <c r="S121" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="122" spans="16:19" x14ac:dyDescent="0.45">
@@ -30754,10 +30793,10 @@
         <v>46</v>
       </c>
       <c r="R122">
-        <v>0.48433333333333328</v>
+        <v>0.48433333333333334</v>
       </c>
       <c r="S122" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="123" spans="16:19" x14ac:dyDescent="0.45">
@@ -30771,7 +30810,7 @@
         <v>0.57599999999999996</v>
       </c>
       <c r="S123" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="124" spans="16:19" x14ac:dyDescent="0.45">
@@ -30785,7 +30824,7 @@
         <v>0.42926666666666669</v>
       </c>
       <c r="S124" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="125" spans="16:19" x14ac:dyDescent="0.45">
@@ -30799,7 +30838,7 @@
         <v>0.42516666666666664</v>
       </c>
       <c r="S125" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="126" spans="16:19" x14ac:dyDescent="0.45">
@@ -30813,7 +30852,7 @@
         <v>0.48203333333333331</v>
       </c>
       <c r="S126" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
